--- a/public/i-1-later/excel/実験1重力加速度エミュレータ.xlsx
+++ b/public/i-1-later/excel/実験1重力加速度エミュレータ.xlsx
@@ -1,23 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="28908"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/278mt/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ogawarinkyuu/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6097CBD9-6B19-C04B-8CB4-3581409EA4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="440" windowWidth="28800" windowHeight="16220" tabRatio="500"/>
+    <workbookView xWindow="4440" yWindow="760" windowWidth="24960" windowHeight="16220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="150001" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="330"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -27,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>測定</t>
     <rPh sb="0" eb="2">
@@ -188,13 +200,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>製作者：とばﾁｬﾝ!（@278Mt）</t>
-    <rPh sb="0" eb="3">
-      <t>セイサクシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>■</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -236,13 +241,6 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>ホウホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>共同制作者：ふくしー</t>
-    <rPh sb="0" eb="5">
-      <t>キョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -250,7 +248,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -580,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -603,7 +601,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
@@ -889,9 +886,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K29"/>
-  <sheetFormatPr baseColWidth="12" defaultColWidth="13.28515625" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.28515625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -903,32 +900,26 @@
     <col min="11" max="13" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="E1" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="22" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="20" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -936,7 +927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="19" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -953,7 +944,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="19" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -973,7 +964,7 @@
         <v>1.563763918802959E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="22" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="20" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -991,7 +982,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="22" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="20" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G7" s="14">
         <f>E29</f>
         <v>1.94913</v>
@@ -1005,7 +996,7 @@
         <v>1.9265000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="19" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1028,7 +1019,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="19" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1</v>
       </c>
@@ -1056,7 +1047,7 @@
         <v>1.3512151192550136E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="22" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="20" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -1069,7 +1060,7 @@
       </c>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="19" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>3</v>
       </c>
@@ -1086,10 +1077,10 @@
       <c r="H11" s="16"/>
       <c r="I11" s="16"/>
       <c r="J11" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>4</v>
       </c>
@@ -1104,13 +1095,12 @@
         <f>4*PI()^2/E29^2*(B6+B15)</f>
         <v>979.15441056938187</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="22"/>
-      <c r="J12" s="23"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J12" s="22"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>5</v>
       </c>
@@ -1125,13 +1115,12 @@
         <f>G12/100</f>
         <v>9.7915441056938182</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="22"/>
-      <c r="J13" s="23"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J13" s="22"/>
+    </row>
+    <row r="14" spans="1:10" ht="19" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>4</v>
       </c>
@@ -1139,14 +1128,12 @@
         <f>AVERAGE(B9:B13)</f>
         <v>3.8530000000000002</v>
       </c>
-      <c r="G14" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="23"/>
-    </row>
-    <row r="15" spans="1:10" ht="22" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G14" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" s="22"/>
+    </row>
+    <row r="15" spans="1:10" ht="20" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1154,23 +1141,23 @@
         <f>B14/2</f>
         <v>1.9265000000000001</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="24">
         <f>G13</f>
         <v>9.7915441056938182</v>
       </c>
-      <c r="H15" s="26" t="s">
+      <c r="H15" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="26">
         <f>J9*G13</f>
         <v>1.3230482436465799E-2</v>
       </c>
-      <c r="J15" s="28" t="s">
+      <c r="J15" s="27" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="22" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:11" ht="21" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="20" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:11" ht="19" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -1195,10 +1182,10 @@
       <c r="H17" s="16"/>
       <c r="I17" s="16"/>
       <c r="J17" s="20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>0</v>
       </c>
@@ -1223,17 +1210,16 @@
         <f>4*PI()^2/E29^2*((B6+B15)+2/5*B15^2/(B6+B15))</f>
         <v>979.31813107720211</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="H18" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="22"/>
-      <c r="J18" s="23"/>
+      <c r="J18" s="22"/>
       <c r="K18">
         <f>($E$29-F18)^2</f>
         <v>4.7089000000000228E-6</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>10</v>
       </c>
@@ -1258,17 +1244,16 @@
         <f>G18/100</f>
         <v>9.7931813107720203</v>
       </c>
-      <c r="H19" s="22" t="s">
+      <c r="H19" t="s">
         <v>12</v>
       </c>
-      <c r="I19" s="22"/>
-      <c r="J19" s="23"/>
+      <c r="J19" s="22"/>
       <c r="K19">
         <f t="shared" ref="K19:K27" si="3">($E$29-F19)^2</f>
         <v>7.5689999999987189E-7</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>20</v>
       </c>
@@ -1289,18 +1274,16 @@
         <f t="shared" si="2"/>
         <v>1.9491000000000001</v>
       </c>
-      <c r="G20" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="23"/>
+      <c r="G20" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="J20" s="22"/>
       <c r="K20">
         <f t="shared" si="3"/>
         <v>8.999999999984695E-10</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>30</v>
       </c>
@@ -1321,18 +1304,18 @@
         <f t="shared" si="2"/>
         <v>1.9486000000000001</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="24">
         <f>G19</f>
         <v>9.7931813107720203</v>
       </c>
-      <c r="H21" s="26" t="s">
+      <c r="H21" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="26">
         <f>J9*G19</f>
         <v>1.3232694652720787E-2</v>
       </c>
-      <c r="J21" s="28" t="s">
+      <c r="J21" s="27" t="s">
         <v>12</v>
       </c>
       <c r="K21">
@@ -1340,7 +1323,7 @@
         <v>2.8089999999991459E-7</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="21" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="19" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>40</v>
       </c>
@@ -1366,7 +1349,7 @@
         <v>5.329000000004986E-7</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>50</v>
       </c>
@@ -1392,7 +1375,7 @@
         <v>1.1449000000007456E-6</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>60</v>
       </c>
@@ -1418,7 +1401,7 @@
         <v>1.060900000000178E-6</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>70</v>
       </c>
@@ -1444,7 +1427,7 @@
         <v>8.9999999998514683E-10</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>80</v>
       </c>
@@ -1470,7 +1453,7 @@
         <v>8.9999999998514683E-10</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>90</v>
       </c>
@@ -1496,7 +1479,7 @@
         <v>2.9929000000008006E-6</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="21" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="19" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>9</v>
       </c>
@@ -1508,7 +1491,7 @@
         <v>1.1481000000002001E-5</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C29">
         <f>AVERAGE(E18:E27)</f>
         <v>194.91300000000001</v>
